--- a/data/trans_dic/IP41-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,16; 97,59</t>
+          <t>91,59; 97,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,98; 95,08</t>
+          <t>87,65; 95,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,88; 89,01</t>
+          <t>78,1; 88,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,62; 96,85</t>
+          <t>90,56; 97,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,25; 91,85</t>
+          <t>83,12; 92,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,54; 95,31</t>
+          <t>87,44; 95,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,5; 96,55</t>
+          <t>92,11; 96,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86,74; 92,48</t>
+          <t>86,97; 92,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84,83; 91,26</t>
+          <t>84,82; 91,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,81; 94,62</t>
+          <t>88,05; 94,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,98; 92,51</t>
+          <t>85,75; 92,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,72; 89,17</t>
+          <t>81,25; 89,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,56; 96,58</t>
+          <t>91,65; 96,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,24; 94,61</t>
+          <t>88,04; 94,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,22; 87,9</t>
+          <t>79,78; 87,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91,17; 94,89</t>
+          <t>91,12; 95,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88,17; 92,77</t>
+          <t>87,94; 92,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81,94; 87,57</t>
+          <t>81,85; 87,54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,57; 95,11</t>
+          <t>87,85; 95,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,4; 93,22</t>
+          <t>85,28; 92,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,47; 88,18</t>
+          <t>79,08; 88,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,79; 95,46</t>
+          <t>88,35; 95,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,05; 91,42</t>
+          <t>83,51; 91,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,5; 83,7</t>
+          <t>73,47; 83,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89,62; 94,48</t>
+          <t>89,47; 94,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,86; 91,28</t>
+          <t>85,64; 91,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77,34; 84,39</t>
+          <t>77,46; 84,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,75; 90,55</t>
+          <t>82,65; 90,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,37; 90,25</t>
+          <t>82,61; 90,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78,0; 87,2</t>
+          <t>77,95; 86,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,63; 91,61</t>
+          <t>84,45; 91,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,57; 88,88</t>
+          <t>80,01; 88,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,52; 85,76</t>
+          <t>76,54; 85,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,88; 90,25</t>
+          <t>84,89; 90,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>82,54; 88,36</t>
+          <t>82,38; 88,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78,45; 85,25</t>
+          <t>78,52; 84,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,21; 92,68</t>
+          <t>89,09; 92,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,23; 91,04</t>
+          <t>87,17; 90,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,72; 86,33</t>
+          <t>81,58; 86,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,57; 93,92</t>
+          <t>90,68; 93,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,16; 90,13</t>
+          <t>86,18; 90,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,43; 85,92</t>
+          <t>81,4; 85,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,55; 92,95</t>
+          <t>90,53; 92,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87,33; 89,99</t>
+          <t>87,36; 90,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82,22; 85,45</t>
+          <t>82,43; 85,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>129645</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>128155</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>112643</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>143466</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>136434</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>136270</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>273111</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>264589</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>248913</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>124728; 133039</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122146; 132426</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>104424; 118542</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>137430; 147496</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>128580; 142442</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>129485; 140820</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>265209; 278068</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>255721; 272404</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>239008; 256945</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>178838</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>184441</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>177666</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>199798</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>205656</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>189359</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>378637</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>390097</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>367025</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>171273; 184294</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>176942; 190699</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>168380; 184794</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>193867; 204516</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>197063; 211263</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>178986; 197158</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>369981; 385907</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>378323; 398545</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>353291; 377825</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>124370</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>138949</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>131177</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>136221</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>146428</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>129861</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>260590</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>285376</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>261037</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>118831; 128652</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>131895; 143812</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123361; 137800</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>130004; 140548</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>139125; 152732</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>121512; 138427</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>252682; 266436</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>275115; 293410</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>248939; 271485</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>178620</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>182179</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>170789</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>181653</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>176714</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>167281</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>360273</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>358893</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>338070</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>169688; 185890</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173738; 189834</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>160992; 179587</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>173305; 188205</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>166728; 185048</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>157463; 175932</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>348500; 370799</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>344942; 369920</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>323722; 350011</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>611473</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>633723</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>592276</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1272611</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1298955</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1215045</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>598015; 623118</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>619496; 646671</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>573893; 606252</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>648912; 671860</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>649341; 679132</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>605264; 638164</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1255626; 1288520</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1279167; 1318438</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1192798; 1236343</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP41-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Habitat-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -519,15 +519,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -632,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,47 +640,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>88,33%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,59; 97,69</t>
+          <t>91,65; 97,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,65; 95,03</t>
+          <t>87,11; 95,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,1; 88,66</t>
+          <t>78,35; 89,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,89; 97,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,56; 97,2</t>
+          <t>83,56; 92,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,12; 92,09</t>
+          <t>87,86; 95,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,44; 95,1</t>
+          <t>92,64; 96,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,01; 92,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,11; 96,57</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>86,97; 92,64</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>84,82; 91,19</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>84,34; 91,09</t>
         </is>
       </c>
     </row>
@@ -804,47 +750,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>90,68%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>85,04%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,05; 94,75</t>
+          <t>88,3; 94,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,75; 92,41</t>
+          <t>85,95; 92,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,25; 89,17</t>
+          <t>81,16; 89,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,96; 96,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,65; 96,69</t>
+          <t>88,21; 94,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,04; 94,38</t>
+          <t>80,5; 88,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,78; 87,88</t>
+          <t>91,15; 95,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,28; 92,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91,12; 95,04</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>87,94; 92,64</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>81,85; 87,54</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>81,85; 87,51</t>
         </is>
       </c>
     </row>
@@ -944,47 +860,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88,83%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>81,22%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,85; 95,11</t>
+          <t>87,53; 94,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,28; 92,99</t>
+          <t>85,84; 93,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,08; 88,33</t>
+          <t>79,46; 88,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>88,76; 95,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88,35; 95,51</t>
+          <t>83,48; 91,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,51; 91,68</t>
+          <t>72,62; 83,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,47; 83,7</t>
+          <t>89,67; 94,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,12; 91,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89,47; 94,34</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85,64; 91,33</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>77,46; 84,47</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>77,54; 84,47</t>
         </is>
       </c>
     </row>
@@ -1084,47 +970,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>85,72%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>82,01%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,65; 90,54</t>
+          <t>82,12; 90,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,61; 90,27</t>
+          <t>82,4; 90,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,95; 86,96</t>
+          <t>77,83; 86,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>84,31; 91,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,45; 91,71</t>
+          <t>80,16; 88,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,01; 88,8</t>
+          <t>76,52; 85,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,54; 85,51</t>
+          <t>84,82; 90,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>82,67; 88,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>84,89; 90,33</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>82,38; 88,35</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>78,52; 84,9</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>78,48; 84,9</t>
         </is>
       </c>
     </row>
@@ -1224,47 +1080,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>88,72%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
           <t>83,97%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,09; 92,83</t>
+          <t>89,0; 92,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,17; 90,99</t>
+          <t>87,29; 91,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,58; 86,18</t>
+          <t>81,96; 86,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,69; 93,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,68; 93,88</t>
+          <t>86,2; 90,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,18; 90,13</t>
+          <t>81,32; 85,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,4; 85,83</t>
+          <t>90,55; 92,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,25; 90,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,53; 92,91</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>87,36; 90,05</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>82,43; 85,44</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>82,42; 85,46</t>
         </is>
       </c>
     </row>
@@ -1345,15 +1171,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1365,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1379,15 +1205,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1398,23 +1221,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1436,47 +1256,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1492,9 +1297,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1524,47 +1326,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>212</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>185</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>401</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>358</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>337</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1592,47 +1379,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>143466</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>143466</t>
+          <t>136434</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>136434</t>
+          <t>136270</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>136270</t>
+          <t>273111</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>264589</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>273111</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>264589</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
           <t>248913</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>124728; 133039</t>
+          <t>124811; 132847</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122146; 132426</t>
+          <t>121397; 132642</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104424; 118542</t>
+          <t>104760; 119313</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>137920; 147345</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>137430; 147496</t>
+          <t>129246; 142492</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>128580; 142442</t>
+          <t>130099; 141049</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>129485; 140820</t>
+          <t>266735; 278776</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>255850; 272330</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>265209; 278068</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>255721; 272404</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>239008; 256945</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>237668; 256663</t>
         </is>
       </c>
     </row>
@@ -1732,47 +1489,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>298</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>282</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>589</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>583</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
           <t>570</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1800,47 +1542,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>199798</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>199798</t>
+          <t>205656</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>205656</t>
+          <t>189359</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>189359</t>
+          <t>378637</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>390097</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>378637</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>390097</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>367025</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>171273; 184294</t>
+          <t>171745; 183915</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>176942; 190699</t>
+          <t>177372; 190364</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>168380; 184794</t>
+          <t>168210; 184887</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>192413; 204134</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>193867; 204516</t>
+          <t>197446; 211587</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>197063; 211263</t>
+          <t>180611; 197512</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>178986; 197158</t>
+          <t>370090; 386158</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>379773; 399059</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>369981; 385907</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>378323; 398545</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353291; 377825</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>353278; 377714</t>
         </is>
       </c>
     </row>
@@ -1940,47 +1652,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>195</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>418</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>440</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>413</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2008,47 +1705,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>136221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>136221</t>
+          <t>146428</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>146428</t>
+          <t>129861</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>129861</t>
+          <t>260590</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285376</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>260590</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>285376</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
           <t>261037</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2061,62 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>118831; 128652</t>
+          <t>118405; 128217</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>131895; 143812</t>
+          <t>132756; 144169</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123361; 137800</t>
+          <t>123960; 137455</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>130613; 140448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>130004; 140548</t>
+          <t>139079; 152612</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>139125; 152732</t>
+          <t>120099; 138160</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>121512; 138427</t>
+          <t>253238; 266570</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>276651; 293349</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>252682; 266436</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>275115; 293410</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>248939; 271485</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>249187; 271487</t>
         </is>
       </c>
     </row>
@@ -2148,47 +1815,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>237</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>501</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>478</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
           <t>469</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2216,47 +1868,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>181653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>181653</t>
+          <t>176714</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>176714</t>
+          <t>167281</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>167281</t>
+          <t>360273</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>358893</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>360273</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>358893</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
           <t>338070</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2269,62 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>169688; 185890</t>
+          <t>168603; 185641</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>173738; 189834</t>
+          <t>173280; 190127</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>160992; 179587</t>
+          <t>160724; 179461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>173003; 187681</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>173305; 188205</t>
+          <t>167051; 184318</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>166728; 185048</t>
+          <t>157431; 175421</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>157463; 175932</t>
+          <t>348188; 370894</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>346122; 370852</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>348500; 370799</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>344942; 369920</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>323722; 350011</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>323541; 349991</t>
         </is>
       </c>
     </row>
@@ -2356,47 +1978,32 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>947</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>893</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
           <t>1789</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2424,47 +2031,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>661138</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>661138</t>
+          <t>665232</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>665232</t>
+          <t>622770</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>622770</t>
+          <t>1272611</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1298955</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1272611</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1298955</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
           <t>1215045</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>598015; 623118</t>
+          <t>597408; 622663</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>619496; 646671</t>
+          <t>620351; 647122</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>573893; 606252</t>
+          <t>576591; 607939</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>648998; 671824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>648912; 671860</t>
+          <t>649515; 678391</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>649341; 679132</t>
+          <t>604626; 638256</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>605264; 638164</t>
+          <t>1255897; 1287529</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1277477; 1317922</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1255626; 1288520</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1279167; 1318438</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>1192798; 1236343</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>1192569; 1236573</t>
         </is>
       </c>
     </row>
@@ -2545,14 +2122,14 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/IP41-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>94,54%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88,2%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>95,2%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>91,96%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>84,25%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>94,54%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>88,2%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91,65; 97,55</t>
+          <t>90,62; 96,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,11; 95,18</t>
+          <t>83,25; 91,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78,35; 89,23</t>
+          <t>87,54; 95,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90,89; 97,1</t>
+          <t>91,16; 97,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,56; 92,12</t>
+          <t>86,98; 95,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,86; 95,25</t>
+          <t>78,88; 89,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,64; 96,82</t>
+          <t>92,5; 96,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,01; 92,62</t>
+          <t>86,74; 92,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>84,34; 91,09</t>
+          <t>84,83; 91,26</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>91,88%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84,4%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>91,94%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>89,38%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>85,73%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>91,88%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>84,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>88,3; 94,55</t>
+          <t>91,56; 96,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,95; 92,25</t>
+          <t>88,24; 94,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,16; 89,21</t>
+          <t>80,22; 87,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90,96; 96,5</t>
+          <t>88,81; 94,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>88,21; 94,53</t>
+          <t>85,98; 92,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,5; 88,03</t>
+          <t>81,72; 89,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,15; 95,1</t>
+          <t>91,17; 94,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,28; 92,76</t>
+          <t>88,17; 92,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,85; 87,51</t>
+          <t>81,94; 87,57</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>87,9%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>78,52%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>91,94%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>89,84%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>84,09%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>92,57%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>78,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,53; 94,78</t>
+          <t>88,79; 95,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,84; 93,22</t>
+          <t>83,05; 91,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,46; 88,11</t>
+          <t>72,5; 83,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,76; 95,44</t>
+          <t>87,57; 95,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,48; 91,61</t>
+          <t>85,4; 93,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>72,62; 83,54</t>
+          <t>79,47; 88,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,67; 94,39</t>
+          <t>89,62; 94,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,12; 91,31</t>
+          <t>85,86; 91,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77,54; 84,47</t>
+          <t>77,34; 84,39</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>88,52%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84,8%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>81,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>87,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>86,63%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>82,7%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>88,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>84,8%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>81,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,12; 90,42</t>
+          <t>84,63; 91,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,4; 90,41</t>
+          <t>80,57; 88,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,83; 86,9</t>
+          <t>76,52; 85,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84,31; 91,46</t>
+          <t>82,75; 90,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>80,16; 88,45</t>
+          <t>82,37; 90,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,52; 85,27</t>
+          <t>78,0; 87,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,82; 90,35</t>
+          <t>84,88; 90,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>82,67; 88,57</t>
+          <t>82,54; 88,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78,48; 84,9</t>
+          <t>78,45; 85,25</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>88,28%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>91,09%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>89,17%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>84,19%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,0; 92,76</t>
+          <t>90,57; 93,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,29; 91,06</t>
+          <t>86,16; 90,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,96; 86,42</t>
+          <t>81,43; 85,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,69; 93,88</t>
+          <t>89,21; 92,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>86,2; 90,03</t>
+          <t>87,23; 91,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,32; 85,84</t>
+          <t>81,72; 86,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,55; 92,83</t>
+          <t>90,55; 92,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>87,25; 90,01</t>
+          <t>87,33; 89,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82,42; 85,46</t>
+          <t>82,22; 85,45</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>158</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>143466</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>136434</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>136270</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>129645</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>128155</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>112643</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>143466</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>136434</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>136270</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>124811; 132847</t>
+          <t>137514; 146969</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>121397; 132642</t>
+          <t>128777; 142074</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>104760; 119313</t>
+          <t>129632; 141138</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>137920; 147345</t>
+          <t>124143; 132897</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>129246; 142492</t>
+          <t>121210; 132501</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>130099; 141049</t>
+          <t>105467; 119018</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>266735; 278776</t>
+          <t>266334; 278003</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>255850; 272330</t>
+          <t>255066; 271938</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>237668; 256663</t>
+          <t>239039; 257155</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>285</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>288</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>199798</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>205656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>189359</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>178838</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>184441</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>177666</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>199798</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>205656</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>189359</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>171745; 183915</t>
+          <t>193670; 204287</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>177372; 190364</t>
+          <t>197517; 211766</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>168210; 184887</t>
+          <t>179985; 197221</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>192413; 204134</t>
+          <t>172738; 184052</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>197446; 211587</t>
+          <t>177436; 190905</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>180611; 197512</t>
+          <t>169368; 184797</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>370090; 386158</t>
+          <t>370201; 385300</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>379773; 399059</t>
+          <t>379289; 399085</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>353278; 377714</t>
+          <t>353676; 377979</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>218</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>136221</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>146428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>129861</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>124370</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>138949</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>131177</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>136221</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>146428</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>129861</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>118405; 128217</t>
+          <t>130655; 140471</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>132756; 144169</t>
+          <t>138353; 152296</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123960; 137455</t>
+          <t>119912; 138425</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>130613; 140448</t>
+          <t>118465; 128654</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>139079; 152612</t>
+          <t>132084; 144169</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>120099; 138160</t>
+          <t>123967; 137555</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>253238; 266570</t>
+          <t>253099; 266829</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>276651; 293349</t>
+          <t>275840; 293238</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>249187; 271487</t>
+          <t>248549; 271217</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>232</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>181653</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>176714</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>167281</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>178620</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>182179</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>170789</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>181653</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>176714</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>167281</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>168603; 185641</t>
+          <t>173668; 187996</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>173280; 190127</t>
+          <t>167907; 185229</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>160724; 179461</t>
+          <t>157438; 176436</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>173003; 187681</t>
+          <t>169897; 185904</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>167051; 184318</t>
+          <t>173225; 189803</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>157431; 175421</t>
+          <t>161089; 180093</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>348188; 370894</t>
+          <t>348443; 370482</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>346122; 370852</t>
+          <t>345606; 369949</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>323541; 349991</t>
+          <t>323434; 351446</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>916</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>912</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>896</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>893</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>611473</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>633723</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>592276</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>661138</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>665232</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>622770</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>597408; 622663</t>
+          <t>648186; 672164</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>620351; 647122</t>
+          <t>649247; 679152</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>576591; 607939</t>
+          <t>605446; 638865</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>648998; 671824</t>
+          <t>598853; 622097</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>649515; 678391</t>
+          <t>619897; 647022</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>604626; 638256</t>
+          <t>574859; 607310</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1255897; 1287529</t>
+          <t>1255890; 1289194</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1277477; 1317922</t>
+          <t>1278637; 1317666</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1192569; 1236573</t>
+          <t>1189699; 1236418</t>
         </is>
       </c>
     </row>
